--- a/docs/excel/01-controles-mcu5-perfil-avanzado.xlsx
+++ b/docs/excel/01-controles-mcu5-perfil-avanzado.xlsx
@@ -786,12 +786,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>docs/11-soa-plan-tratamiento (pendiente). Este Excel es la base de la brecha MCU.</t>
+          <t>docs/11-soa-plan-tratamiento.md (93 controles ISO: 68 aplican, 25 N.A.). Este Excel es la base de la brecha MCU.</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Keycloak (A12) corre sin realm ni usuarios. docs/09-gestion-accesos.md define la política (borrador 07/10).</t>
+          <t>Keycloak (A12) corre con certificados TLS propios (infra/identity/certs/, commit 40364c8) pero todavía sin realm ni usuarios. docs/09-gestion-accesos.md define la política.</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>RF-12. MFA en Keycloak sin configurar. Dashboard de Wazuh hoy sin login (A08): brecha.</t>
+          <t>RF-12. MFA en Keycloak sin configurar (TLS de base lista). Dashboard de Wazuh hoy sin login (A08): brecha.</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>TLS: solo mail (autofirmado). Keycloak en HTTP (KC_HTTP_ENABLED), indexer sin TLS interno (plugin de seguridad desactivado), bases sin cifrado en reposo. Tratar o justificar en docs/03.</t>
+          <t>TLS: mail (autofirmado) + Keycloak (certs propios, commit 40364c8). Indexer sin TLS interno (plugin de seguridad desactivado), bases sin cifrado en reposo. Tratar o justificar en docs/03.</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Agente Wazuh embebido en target-ssh-client (A05), sin verificar conexión. Falta en target-webapp (CU-03).</t>
+          <t>Agentes Wazuh verificados en target-ssh-client (CU-02, 11/10) y target-webapp (CU-03, 11/10). Evidencia en docs/evidencias/CU-02 y CU-03_INC-2026-003.</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Agente en A05 (sin verificar). FIM sobre el webroot de la app (CU-03): pendiente.</t>
+          <t>FIM verificado sobre /var/www/html de target-webapp (CU-03, 11/10): detecta alta de archivo PHP y dispara regla local 100200. Evidencia en docs/evidencias/CU-03_INC-2026-003.</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>CU-01 ejecutado y detectado (INC-2026-001). CU-02 y CU-03 pendientes. Red Team: 28/10-09/11.</t>
+          <t>CU-01, CU-02 y CU-03 ejecutados y detectados con evidencia (docs/evidencias/). Red Team: 28/10-09/11.</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>INC-2026-001 cerrado (detección; sin contención por diseño). Contención automática de CU-02 sin verificar.</t>
+          <t>INC-2026-001 cerrado (detección). INC-2026-002 cerrado con contención automática verificada (firewall-drop). INC-2026-003 cerrado con aislamiento automático verificado (isolate-webapp).</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Sin incidente con erradicación ejecutada todavía (CU-02/CU-03).</t>
+          <t>CU-02: IP atacante bloqueada por Active Response (verificado con timeout de reconexión). CU-03: contenedor aislado de red preservando TCP 1514 al manager. Evidencia en docs/evidencias/.</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>docs/12 (pendiente). Plazos BCU/URCDP a confirmar (docs/04 §4).</t>
+          <t>docs/12-notificacion-incidentes.md: ejercicio de escritorio completo (INC-2026-004, BCU+URCDP). Plazos legales BCU/URCDP a confirmar.</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>docs/06-plan-continuidad (pendiente), con RTO/RPO.</t>
+          <t>docs/06-plan-continuidad.md: RTO/RPO definidos, inventario de respaldo definido. Prueba de restauración: no ejecutada.</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>A definir en docs/06.</t>
+          <t>docs/06-plan-continuidad.md §5: canales y responsables de comunicación de crisis definidos.</t>
         </is>
       </c>
     </row>

--- a/docs/excel/01-controles-mcu5-perfil-avanzado.xlsx
+++ b/docs/excel/01-controles-mcu5-perfil-avanzado.xlsx
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>CU-01, CU-02 y CU-03 ejecutados y detectados con evidencia (docs/evidencias/). Red Team: 28/10-09/11.</t>
+          <t>CU-01, CU-02 y CU-03 ejecutados y verificados de punta a punta (deteccion -&gt; respuesta -&gt; notificacion), con evidencia en docs/evidencias/. Red Team: 28/10-09/11.</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Mail automático a soc@lab.local para nivel ≥10 (configurado). Sin captura de un mail recibido. 2º canal (webhook/Wazo) recortado con justificación.</t>
+          <t>Mail automático a soc@lab.local para nivel &gt;=10, verificado de punta a punta en CU-02 (nivel 10) y CU-03 (nivel 12) el 14/10. 2do canal (webhook/Wazo) recortado con justificacion.</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>INC-2026-001 cerrado (detección). INC-2026-002 cerrado con contención automática verificada (firewall-drop). INC-2026-003 cerrado con aislamiento automático verificado (isolate-webapp).</t>
+          <t>INC-2026-001 cerrado (deteccion). INC-2026-002 y INC-2026-003 cerrados con contencion automatica y notificacion verificadas de punta a punta (14/10).</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>CU-02: IP atacante bloqueada por Active Response (verificado con timeout de reconexión). CU-03: contenedor aislado de red preservando TCP 1514 al manager. Evidencia en docs/evidencias/.</t>
+          <t>CU-02: IP atacante bloqueada por Active Response, verificado con timestamps reales (MTTR ~0s). CU-03: contenedor aislado preservando TCP 1514 al manager, verificado con timestamps reales (MTTR ~0s). Evidencia en docs/evidencias/.</t>
         </is>
       </c>
     </row>
